--- a/other resources/provident fund 2024-25.xlsx
+++ b/other resources/provident fund 2024-25.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28129"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C15D5EF3-D99C-442D-9A6E-6CC8F7AC283D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
   </bookViews>
   <sheets>
     <sheet name="Main File" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -26,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="68">
   <si>
     <t>SL</t>
   </si>
@@ -228,11 +227,14 @@
   <si>
     <t>BIDS Provident Fund for the F/Y 2023-24 (01.07.2023 to 30.06.2024)</t>
   </si>
+  <si>
+    <t>Mr. Abdullah Al Mamun, OA</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
@@ -566,9 +568,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -606,9 +608,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -643,7 +645,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -678,7 +680,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -851,7 +853,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -17318,10 +17320,10 @@
     </row>
     <row r="116" spans="1:60" x14ac:dyDescent="0.2">
       <c r="A116" s="23">
-        <v>4103</v>
+        <v>106</v>
       </c>
       <c r="B116" s="23">
-        <v>4103</v>
+        <v>1403</v>
       </c>
       <c r="C116" s="3" t="s">
         <v>64</v>
@@ -17654,10 +17656,10 @@
         <v>108</v>
       </c>
       <c r="B118" s="23">
-        <v>108</v>
+        <v>4103</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>27</v>
+        <v>67</v>
       </c>
       <c r="D118" s="14">
         <v>30684</v>

--- a/other resources/provident fund 2024-25.xlsx
+++ b/other resources/provident fund 2024-25.xlsx
@@ -480,6 +480,42 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -498,17 +534,11 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -518,36 +548,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -934,326 +934,326 @@
       <c r="Z1" s="3"/>
     </row>
     <row r="2" spans="1:60" x14ac:dyDescent="0.2">
-      <c r="A2" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="39" t="s">
+      <c r="A2" s="41" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="49" t="s">
         <v>65</v>
       </c>
-      <c r="C2" s="30" t="s">
+      <c r="C2" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="31" t="s">
+      <c r="D2" s="43" t="s">
         <v>66</v>
       </c>
-      <c r="E2" s="31"/>
-      <c r="F2" s="31"/>
-      <c r="G2" s="31"/>
-      <c r="H2" s="31"/>
-      <c r="I2" s="31"/>
-      <c r="J2" s="31"/>
-      <c r="K2" s="31"/>
-      <c r="L2" s="32" t="s">
+      <c r="E2" s="43"/>
+      <c r="F2" s="43"/>
+      <c r="G2" s="43"/>
+      <c r="H2" s="43"/>
+      <c r="I2" s="43"/>
+      <c r="J2" s="43"/>
+      <c r="K2" s="43"/>
+      <c r="L2" s="44" t="s">
         <v>58</v>
       </c>
-      <c r="M2" s="32"/>
-      <c r="N2" s="32"/>
-      <c r="O2" s="32"/>
-      <c r="P2" s="32"/>
-      <c r="Q2" s="32"/>
-      <c r="R2" s="32"/>
-      <c r="S2" s="32"/>
-      <c r="T2" s="32"/>
-      <c r="U2" s="32"/>
-      <c r="V2" s="32"/>
-      <c r="W2" s="32"/>
-      <c r="X2" s="32"/>
-      <c r="Y2" s="32"/>
-      <c r="Z2" s="32"/>
-      <c r="AA2" s="33" t="s">
+      <c r="M2" s="44"/>
+      <c r="N2" s="44"/>
+      <c r="O2" s="44"/>
+      <c r="P2" s="44"/>
+      <c r="Q2" s="44"/>
+      <c r="R2" s="44"/>
+      <c r="S2" s="44"/>
+      <c r="T2" s="44"/>
+      <c r="U2" s="44"/>
+      <c r="V2" s="44"/>
+      <c r="W2" s="44"/>
+      <c r="X2" s="44"/>
+      <c r="Y2" s="44"/>
+      <c r="Z2" s="44"/>
+      <c r="AA2" s="45" t="s">
         <v>50</v>
       </c>
-      <c r="AB2" s="33"/>
-      <c r="AC2" s="33"/>
-      <c r="AD2" s="33"/>
-      <c r="AE2" s="33"/>
-      <c r="AF2" s="33"/>
-      <c r="AG2" s="33"/>
-      <c r="AH2" s="33"/>
-      <c r="AI2" s="33"/>
-      <c r="AJ2" s="33"/>
-      <c r="AK2" s="33"/>
-      <c r="AL2" s="33"/>
-      <c r="AM2" s="42" t="s">
+      <c r="AB2" s="45"/>
+      <c r="AC2" s="45"/>
+      <c r="AD2" s="45"/>
+      <c r="AE2" s="45"/>
+      <c r="AF2" s="45"/>
+      <c r="AG2" s="45"/>
+      <c r="AH2" s="45"/>
+      <c r="AI2" s="45"/>
+      <c r="AJ2" s="45"/>
+      <c r="AK2" s="45"/>
+      <c r="AL2" s="45"/>
+      <c r="AM2" s="35" t="s">
         <v>32</v>
       </c>
-      <c r="AN2" s="42" t="s">
+      <c r="AN2" s="35" t="s">
         <v>33</v>
       </c>
-      <c r="AO2" s="42" t="s">
+      <c r="AO2" s="35" t="s">
         <v>34</v>
       </c>
-      <c r="AP2" s="42" t="s">
+      <c r="AP2" s="35" t="s">
         <v>35</v>
       </c>
-      <c r="AQ2" s="48" t="s">
+      <c r="AQ2" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="AR2" s="48"/>
-      <c r="AS2" s="48"/>
-      <c r="AT2" s="48"/>
-      <c r="AU2" s="48"/>
-      <c r="AV2" s="48"/>
-      <c r="AW2" s="48"/>
-      <c r="AX2" s="48"/>
-      <c r="AY2" s="48"/>
-      <c r="AZ2" s="48"/>
-      <c r="BA2" s="48"/>
-      <c r="BB2" s="48"/>
-      <c r="BC2" s="49" t="s">
+      <c r="AR2" s="31"/>
+      <c r="AS2" s="31"/>
+      <c r="AT2" s="31"/>
+      <c r="AU2" s="31"/>
+      <c r="AV2" s="31"/>
+      <c r="AW2" s="31"/>
+      <c r="AX2" s="31"/>
+      <c r="AY2" s="31"/>
+      <c r="AZ2" s="31"/>
+      <c r="BA2" s="31"/>
+      <c r="BB2" s="31"/>
+      <c r="BC2" s="32" t="s">
         <v>60</v>
       </c>
-      <c r="BD2" s="47" t="s">
+      <c r="BD2" s="30" t="s">
         <v>61</v>
       </c>
-      <c r="BE2" s="47" t="s">
+      <c r="BE2" s="30" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="3" spans="1:60" x14ac:dyDescent="0.2">
-      <c r="A3" s="29"/>
-      <c r="B3" s="40"/>
-      <c r="C3" s="30"/>
-      <c r="D3" s="43" t="s">
+      <c r="A3" s="41"/>
+      <c r="B3" s="50"/>
+      <c r="C3" s="42"/>
+      <c r="D3" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="43"/>
-      <c r="F3" s="43"/>
-      <c r="G3" s="43" t="s">
+      <c r="E3" s="36"/>
+      <c r="F3" s="36"/>
+      <c r="G3" s="36" t="s">
         <v>3</v>
       </c>
-      <c r="H3" s="43"/>
+      <c r="H3" s="36"/>
       <c r="I3" s="5"/>
       <c r="J3" s="5"/>
       <c r="K3" s="5"/>
-      <c r="L3" s="32"/>
-      <c r="M3" s="32"/>
-      <c r="N3" s="32"/>
-      <c r="O3" s="32"/>
-      <c r="P3" s="32"/>
-      <c r="Q3" s="32"/>
-      <c r="R3" s="32"/>
-      <c r="S3" s="32"/>
-      <c r="T3" s="32"/>
-      <c r="U3" s="32"/>
-      <c r="V3" s="32"/>
-      <c r="W3" s="32"/>
-      <c r="X3" s="32"/>
-      <c r="Y3" s="32"/>
-      <c r="Z3" s="32"/>
-      <c r="AA3" s="33"/>
-      <c r="AB3" s="33"/>
-      <c r="AC3" s="33"/>
-      <c r="AD3" s="33"/>
-      <c r="AE3" s="33"/>
-      <c r="AF3" s="33"/>
-      <c r="AG3" s="33"/>
-      <c r="AH3" s="33"/>
-      <c r="AI3" s="33"/>
-      <c r="AJ3" s="33"/>
-      <c r="AK3" s="33"/>
-      <c r="AL3" s="33"/>
-      <c r="AM3" s="42"/>
-      <c r="AN3" s="42"/>
-      <c r="AO3" s="42"/>
-      <c r="AP3" s="42"/>
-      <c r="AQ3" s="48"/>
-      <c r="AR3" s="48"/>
-      <c r="AS3" s="48"/>
-      <c r="AT3" s="48"/>
-      <c r="AU3" s="48"/>
-      <c r="AV3" s="48"/>
-      <c r="AW3" s="48"/>
-      <c r="AX3" s="48"/>
-      <c r="AY3" s="48"/>
-      <c r="AZ3" s="48"/>
-      <c r="BA3" s="48"/>
-      <c r="BB3" s="48"/>
-      <c r="BC3" s="50"/>
-      <c r="BD3" s="47"/>
-      <c r="BE3" s="47"/>
+      <c r="L3" s="44"/>
+      <c r="M3" s="44"/>
+      <c r="N3" s="44"/>
+      <c r="O3" s="44"/>
+      <c r="P3" s="44"/>
+      <c r="Q3" s="44"/>
+      <c r="R3" s="44"/>
+      <c r="S3" s="44"/>
+      <c r="T3" s="44"/>
+      <c r="U3" s="44"/>
+      <c r="V3" s="44"/>
+      <c r="W3" s="44"/>
+      <c r="X3" s="44"/>
+      <c r="Y3" s="44"/>
+      <c r="Z3" s="44"/>
+      <c r="AA3" s="45"/>
+      <c r="AB3" s="45"/>
+      <c r="AC3" s="45"/>
+      <c r="AD3" s="45"/>
+      <c r="AE3" s="45"/>
+      <c r="AF3" s="45"/>
+      <c r="AG3" s="45"/>
+      <c r="AH3" s="45"/>
+      <c r="AI3" s="45"/>
+      <c r="AJ3" s="45"/>
+      <c r="AK3" s="45"/>
+      <c r="AL3" s="45"/>
+      <c r="AM3" s="35"/>
+      <c r="AN3" s="35"/>
+      <c r="AO3" s="35"/>
+      <c r="AP3" s="35"/>
+      <c r="AQ3" s="31"/>
+      <c r="AR3" s="31"/>
+      <c r="AS3" s="31"/>
+      <c r="AT3" s="31"/>
+      <c r="AU3" s="31"/>
+      <c r="AV3" s="31"/>
+      <c r="AW3" s="31"/>
+      <c r="AX3" s="31"/>
+      <c r="AY3" s="31"/>
+      <c r="AZ3" s="31"/>
+      <c r="BA3" s="31"/>
+      <c r="BB3" s="31"/>
+      <c r="BC3" s="33"/>
+      <c r="BD3" s="30"/>
+      <c r="BE3" s="30"/>
     </row>
     <row r="4" spans="1:60" x14ac:dyDescent="0.2">
-      <c r="A4" s="29"/>
-      <c r="B4" s="40"/>
-      <c r="C4" s="30"/>
-      <c r="D4" s="35" t="s">
+      <c r="A4" s="41"/>
+      <c r="B4" s="50"/>
+      <c r="C4" s="42"/>
+      <c r="D4" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="35" t="s">
+      <c r="E4" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="F4" s="35" t="s">
+      <c r="F4" s="37" t="s">
         <v>36</v>
       </c>
-      <c r="G4" s="35" t="s">
+      <c r="G4" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="H4" s="35" t="s">
+      <c r="H4" s="37" t="s">
         <v>63</v>
       </c>
-      <c r="I4" s="35" t="s">
+      <c r="I4" s="37" t="s">
         <v>54</v>
       </c>
-      <c r="J4" s="35" t="s">
+      <c r="J4" s="37" t="s">
         <v>55</v>
       </c>
-      <c r="K4" s="35" t="s">
+      <c r="K4" s="37" t="s">
         <v>56</v>
       </c>
-      <c r="L4" s="36" t="s">
+      <c r="L4" s="47" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="37" t="s">
+      <c r="M4" s="48" t="s">
         <v>8</v>
       </c>
-      <c r="N4" s="37"/>
-      <c r="O4" s="37"/>
-      <c r="P4" s="37"/>
-      <c r="Q4" s="37"/>
-      <c r="R4" s="37"/>
-      <c r="S4" s="37"/>
-      <c r="T4" s="37"/>
-      <c r="U4" s="37"/>
-      <c r="V4" s="37"/>
-      <c r="W4" s="37"/>
-      <c r="X4" s="37"/>
+      <c r="N4" s="48"/>
+      <c r="O4" s="48"/>
+      <c r="P4" s="48"/>
+      <c r="Q4" s="48"/>
+      <c r="R4" s="48"/>
+      <c r="S4" s="48"/>
+      <c r="T4" s="48"/>
+      <c r="U4" s="48"/>
+      <c r="V4" s="48"/>
+      <c r="W4" s="48"/>
+      <c r="X4" s="48"/>
       <c r="Y4" s="38" t="s">
         <v>9</v>
       </c>
       <c r="Z4" s="38" t="s">
         <v>10</v>
       </c>
-      <c r="AA4" s="34"/>
-      <c r="AB4" s="34"/>
-      <c r="AC4" s="34"/>
-      <c r="AD4" s="34"/>
-      <c r="AE4" s="34"/>
-      <c r="AF4" s="34"/>
-      <c r="AG4" s="34"/>
-      <c r="AH4" s="34"/>
-      <c r="AI4" s="34"/>
-      <c r="AJ4" s="34"/>
-      <c r="AK4" s="34"/>
-      <c r="AL4" s="34"/>
-      <c r="AM4" s="42"/>
-      <c r="AN4" s="42"/>
-      <c r="AO4" s="42"/>
-      <c r="AP4" s="42"/>
-      <c r="AQ4" s="48"/>
-      <c r="AR4" s="48"/>
-      <c r="AS4" s="48"/>
-      <c r="AT4" s="48"/>
-      <c r="AU4" s="48"/>
-      <c r="AV4" s="48"/>
-      <c r="AW4" s="48"/>
-      <c r="AX4" s="48"/>
-      <c r="AY4" s="48"/>
-      <c r="AZ4" s="48"/>
-      <c r="BA4" s="48"/>
-      <c r="BB4" s="48"/>
-      <c r="BC4" s="50"/>
-      <c r="BD4" s="47"/>
-      <c r="BE4" s="47"/>
+      <c r="AA4" s="46"/>
+      <c r="AB4" s="46"/>
+      <c r="AC4" s="46"/>
+      <c r="AD4" s="46"/>
+      <c r="AE4" s="46"/>
+      <c r="AF4" s="46"/>
+      <c r="AG4" s="46"/>
+      <c r="AH4" s="46"/>
+      <c r="AI4" s="46"/>
+      <c r="AJ4" s="46"/>
+      <c r="AK4" s="46"/>
+      <c r="AL4" s="46"/>
+      <c r="AM4" s="35"/>
+      <c r="AN4" s="35"/>
+      <c r="AO4" s="35"/>
+      <c r="AP4" s="35"/>
+      <c r="AQ4" s="31"/>
+      <c r="AR4" s="31"/>
+      <c r="AS4" s="31"/>
+      <c r="AT4" s="31"/>
+      <c r="AU4" s="31"/>
+      <c r="AV4" s="31"/>
+      <c r="AW4" s="31"/>
+      <c r="AX4" s="31"/>
+      <c r="AY4" s="31"/>
+      <c r="AZ4" s="31"/>
+      <c r="BA4" s="31"/>
+      <c r="BB4" s="31"/>
+      <c r="BC4" s="33"/>
+      <c r="BD4" s="30"/>
+      <c r="BE4" s="30"/>
     </row>
     <row r="5" spans="1:60" x14ac:dyDescent="0.2">
-      <c r="A5" s="29"/>
-      <c r="B5" s="40"/>
-      <c r="C5" s="30"/>
-      <c r="D5" s="35"/>
-      <c r="E5" s="35"/>
-      <c r="F5" s="35"/>
-      <c r="G5" s="35"/>
-      <c r="H5" s="35"/>
-      <c r="I5" s="35"/>
-      <c r="J5" s="35"/>
-      <c r="K5" s="35"/>
-      <c r="L5" s="36"/>
-      <c r="M5" s="37"/>
-      <c r="N5" s="37"/>
-      <c r="O5" s="37"/>
-      <c r="P5" s="37"/>
-      <c r="Q5" s="37"/>
-      <c r="R5" s="37"/>
-      <c r="S5" s="37"/>
-      <c r="T5" s="37"/>
-      <c r="U5" s="37"/>
-      <c r="V5" s="37"/>
-      <c r="W5" s="37"/>
-      <c r="X5" s="37"/>
+      <c r="A5" s="41"/>
+      <c r="B5" s="50"/>
+      <c r="C5" s="42"/>
+      <c r="D5" s="37"/>
+      <c r="E5" s="37"/>
+      <c r="F5" s="37"/>
+      <c r="G5" s="37"/>
+      <c r="H5" s="37"/>
+      <c r="I5" s="37"/>
+      <c r="J5" s="37"/>
+      <c r="K5" s="37"/>
+      <c r="L5" s="47"/>
+      <c r="M5" s="48"/>
+      <c r="N5" s="48"/>
+      <c r="O5" s="48"/>
+      <c r="P5" s="48"/>
+      <c r="Q5" s="48"/>
+      <c r="R5" s="48"/>
+      <c r="S5" s="48"/>
+      <c r="T5" s="48"/>
+      <c r="U5" s="48"/>
+      <c r="V5" s="48"/>
+      <c r="W5" s="48"/>
+      <c r="X5" s="48"/>
       <c r="Y5" s="38"/>
       <c r="Z5" s="38"/>
-      <c r="AA5" s="44" t="s">
+      <c r="AA5" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="AB5" s="44"/>
-      <c r="AC5" s="44"/>
-      <c r="AD5" s="44"/>
-      <c r="AE5" s="44"/>
-      <c r="AF5" s="44"/>
-      <c r="AG5" s="44"/>
-      <c r="AH5" s="44"/>
-      <c r="AI5" s="44"/>
-      <c r="AJ5" s="44"/>
-      <c r="AK5" s="44"/>
-      <c r="AL5" s="44"/>
-      <c r="AM5" s="42"/>
-      <c r="AN5" s="42"/>
-      <c r="AO5" s="42"/>
-      <c r="AP5" s="42"/>
-      <c r="AQ5" s="48"/>
-      <c r="AR5" s="48"/>
-      <c r="AS5" s="48"/>
-      <c r="AT5" s="48"/>
-      <c r="AU5" s="48"/>
-      <c r="AV5" s="48"/>
-      <c r="AW5" s="48"/>
-      <c r="AX5" s="48"/>
-      <c r="AY5" s="48"/>
-      <c r="AZ5" s="48"/>
-      <c r="BA5" s="48"/>
-      <c r="BB5" s="48"/>
-      <c r="BC5" s="50"/>
-      <c r="BD5" s="47"/>
-      <c r="BE5" s="47"/>
+      <c r="AB5" s="39"/>
+      <c r="AC5" s="39"/>
+      <c r="AD5" s="39"/>
+      <c r="AE5" s="39"/>
+      <c r="AF5" s="39"/>
+      <c r="AG5" s="39"/>
+      <c r="AH5" s="39"/>
+      <c r="AI5" s="39"/>
+      <c r="AJ5" s="39"/>
+      <c r="AK5" s="39"/>
+      <c r="AL5" s="39"/>
+      <c r="AM5" s="35"/>
+      <c r="AN5" s="35"/>
+      <c r="AO5" s="35"/>
+      <c r="AP5" s="35"/>
+      <c r="AQ5" s="31"/>
+      <c r="AR5" s="31"/>
+      <c r="AS5" s="31"/>
+      <c r="AT5" s="31"/>
+      <c r="AU5" s="31"/>
+      <c r="AV5" s="31"/>
+      <c r="AW5" s="31"/>
+      <c r="AX5" s="31"/>
+      <c r="AY5" s="31"/>
+      <c r="AZ5" s="31"/>
+      <c r="BA5" s="31"/>
+      <c r="BB5" s="31"/>
+      <c r="BC5" s="33"/>
+      <c r="BD5" s="30"/>
+      <c r="BE5" s="30"/>
     </row>
     <row r="6" spans="1:60" x14ac:dyDescent="0.2">
-      <c r="A6" s="29"/>
-      <c r="B6" s="40"/>
-      <c r="C6" s="30"/>
-      <c r="D6" s="35"/>
-      <c r="E6" s="35"/>
-      <c r="F6" s="35"/>
-      <c r="G6" s="35"/>
-      <c r="H6" s="35"/>
-      <c r="I6" s="35"/>
-      <c r="J6" s="35"/>
-      <c r="K6" s="35"/>
-      <c r="L6" s="36"/>
-      <c r="M6" s="45" t="s">
+      <c r="A6" s="41"/>
+      <c r="B6" s="50"/>
+      <c r="C6" s="42"/>
+      <c r="D6" s="37"/>
+      <c r="E6" s="37"/>
+      <c r="F6" s="37"/>
+      <c r="G6" s="37"/>
+      <c r="H6" s="37"/>
+      <c r="I6" s="37"/>
+      <c r="J6" s="37"/>
+      <c r="K6" s="37"/>
+      <c r="L6" s="47"/>
+      <c r="M6" s="40" t="s">
         <v>11</v>
       </c>
-      <c r="N6" s="45"/>
-      <c r="O6" s="45"/>
-      <c r="P6" s="45"/>
-      <c r="Q6" s="45"/>
-      <c r="R6" s="45"/>
-      <c r="S6" s="45"/>
-      <c r="T6" s="45"/>
-      <c r="U6" s="45"/>
-      <c r="V6" s="45"/>
-      <c r="W6" s="45"/>
-      <c r="X6" s="45"/>
+      <c r="N6" s="40"/>
+      <c r="O6" s="40"/>
+      <c r="P6" s="40"/>
+      <c r="Q6" s="40"/>
+      <c r="R6" s="40"/>
+      <c r="S6" s="40"/>
+      <c r="T6" s="40"/>
+      <c r="U6" s="40"/>
+      <c r="V6" s="40"/>
+      <c r="W6" s="40"/>
+      <c r="X6" s="40"/>
       <c r="Y6" s="38"/>
       <c r="Z6" s="38"/>
       <c r="AA6" s="6" t="s">
@@ -1292,40 +1292,40 @@
       <c r="AL6" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="AM6" s="42"/>
-      <c r="AN6" s="42"/>
-      <c r="AO6" s="42"/>
-      <c r="AP6" s="42"/>
-      <c r="AQ6" s="46" t="s">
+      <c r="AM6" s="35"/>
+      <c r="AN6" s="35"/>
+      <c r="AO6" s="35"/>
+      <c r="AP6" s="35"/>
+      <c r="AQ6" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="AR6" s="46"/>
-      <c r="AS6" s="46"/>
-      <c r="AT6" s="46"/>
-      <c r="AU6" s="46"/>
-      <c r="AV6" s="46"/>
-      <c r="AW6" s="46"/>
-      <c r="AX6" s="46"/>
-      <c r="AY6" s="46"/>
-      <c r="AZ6" s="46"/>
-      <c r="BA6" s="46"/>
-      <c r="BB6" s="46"/>
-      <c r="BC6" s="50"/>
-      <c r="BD6" s="47"/>
-      <c r="BE6" s="47"/>
+      <c r="AR6" s="29"/>
+      <c r="AS6" s="29"/>
+      <c r="AT6" s="29"/>
+      <c r="AU6" s="29"/>
+      <c r="AV6" s="29"/>
+      <c r="AW6" s="29"/>
+      <c r="AX6" s="29"/>
+      <c r="AY6" s="29"/>
+      <c r="AZ6" s="29"/>
+      <c r="BA6" s="29"/>
+      <c r="BB6" s="29"/>
+      <c r="BC6" s="33"/>
+      <c r="BD6" s="30"/>
+      <c r="BE6" s="30"/>
     </row>
     <row r="7" spans="1:60" x14ac:dyDescent="0.2">
-      <c r="A7" s="29"/>
-      <c r="B7" s="41"/>
-      <c r="C7" s="30"/>
-      <c r="D7" s="35"/>
-      <c r="E7" s="35"/>
-      <c r="F7" s="35"/>
-      <c r="G7" s="35"/>
-      <c r="H7" s="35"/>
-      <c r="I7" s="35"/>
-      <c r="J7" s="35"/>
-      <c r="K7" s="35"/>
+      <c r="A7" s="41"/>
+      <c r="B7" s="51"/>
+      <c r="C7" s="42"/>
+      <c r="D7" s="37"/>
+      <c r="E7" s="37"/>
+      <c r="F7" s="37"/>
+      <c r="G7" s="37"/>
+      <c r="H7" s="37"/>
+      <c r="I7" s="37"/>
+      <c r="J7" s="37"/>
+      <c r="K7" s="37"/>
       <c r="L7" s="27" t="s">
         <v>57</v>
       </c>
@@ -1407,10 +1407,10 @@
       <c r="AL7" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="AM7" s="42"/>
-      <c r="AN7" s="42"/>
-      <c r="AO7" s="42"/>
-      <c r="AP7" s="42"/>
+      <c r="AM7" s="35"/>
+      <c r="AN7" s="35"/>
+      <c r="AO7" s="35"/>
+      <c r="AP7" s="35"/>
       <c r="AQ7" s="13" t="s">
         <v>38</v>
       </c>
@@ -1447,9 +1447,9 @@
       <c r="BB7" s="28" t="s">
         <v>49</v>
       </c>
-      <c r="BC7" s="51"/>
-      <c r="BD7" s="47"/>
-      <c r="BE7" s="47"/>
+      <c r="BC7" s="34"/>
+      <c r="BD7" s="30"/>
+      <c r="BE7" s="30"/>
     </row>
     <row r="8" spans="1:60" x14ac:dyDescent="0.2">
       <c r="A8" s="23">
@@ -17323,7 +17323,7 @@
         <v>106</v>
       </c>
       <c r="B116" s="23">
-        <v>1403</v>
+        <v>1503</v>
       </c>
       <c r="C116" s="3" t="s">
         <v>64</v>
@@ -17792,11 +17792,18 @@
     </row>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="AQ6:BB6"/>
-    <mergeCell ref="BE2:BE7"/>
-    <mergeCell ref="AQ2:BB5"/>
-    <mergeCell ref="BC2:BC7"/>
-    <mergeCell ref="BD2:BD7"/>
+    <mergeCell ref="A2:A7"/>
+    <mergeCell ref="C2:C7"/>
+    <mergeCell ref="D2:K2"/>
+    <mergeCell ref="L2:Z3"/>
+    <mergeCell ref="AA2:AL4"/>
+    <mergeCell ref="K4:K7"/>
+    <mergeCell ref="L4:L6"/>
+    <mergeCell ref="M4:X5"/>
+    <mergeCell ref="Y4:Y6"/>
+    <mergeCell ref="I4:I7"/>
+    <mergeCell ref="J4:J7"/>
+    <mergeCell ref="B2:B7"/>
     <mergeCell ref="AN2:AN7"/>
     <mergeCell ref="AO2:AO7"/>
     <mergeCell ref="AP2:AP7"/>
@@ -17811,18 +17818,11 @@
     <mergeCell ref="Z4:Z6"/>
     <mergeCell ref="AA5:AL5"/>
     <mergeCell ref="M6:X6"/>
-    <mergeCell ref="A2:A7"/>
-    <mergeCell ref="C2:C7"/>
-    <mergeCell ref="D2:K2"/>
-    <mergeCell ref="L2:Z3"/>
-    <mergeCell ref="AA2:AL4"/>
-    <mergeCell ref="K4:K7"/>
-    <mergeCell ref="L4:L6"/>
-    <mergeCell ref="M4:X5"/>
-    <mergeCell ref="Y4:Y6"/>
-    <mergeCell ref="I4:I7"/>
-    <mergeCell ref="J4:J7"/>
-    <mergeCell ref="B2:B7"/>
+    <mergeCell ref="AQ6:BB6"/>
+    <mergeCell ref="BE2:BE7"/>
+    <mergeCell ref="AQ2:BB5"/>
+    <mergeCell ref="BC2:BC7"/>
+    <mergeCell ref="BD2:BD7"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
